--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 02/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.83067</v>
+        <v>16.8656</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52572</v>
+        <v>16.44457</v>
       </c>
       <c r="E2" t="n">
-        <v>16.25542</v>
+        <v>16.5213</v>
       </c>
       <c r="F2" t="n">
-        <v>42.28797</v>
+        <v>42.3712</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05087</v>
+        <v>0.05065</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81835</v>
+        <v>1.79183</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.69272</v>
+        <v>16.64239</v>
       </c>
       <c r="D3" t="n">
-        <v>16.59657</v>
+        <v>16.54032</v>
       </c>
       <c r="E3" t="n">
-        <v>16.53943</v>
+        <v>16.57808</v>
       </c>
       <c r="F3" t="n">
-        <v>42.06426</v>
+        <v>42.35931</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04996</v>
+        <v>0.04882</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83571</v>
+        <v>1.80551</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.55489</v>
+        <v>16.70551</v>
       </c>
       <c r="D4" t="n">
-        <v>16.74014</v>
+        <v>16.21743</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72554</v>
+        <v>16.67368</v>
       </c>
       <c r="F4" t="n">
-        <v>42.72513</v>
+        <v>42.62177</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05056</v>
+        <v>0.05107</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82465</v>
+        <v>1.81665</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.43583</v>
+        <v>16.62749</v>
       </c>
       <c r="D6" t="n">
-        <v>16.11316</v>
+        <v>15.92154</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30875</v>
+        <v>16.47348</v>
       </c>
       <c r="F6" t="n">
-        <v>21.38119</v>
+        <v>22.03259</v>
       </c>
       <c r="G6" t="n">
-        <v>33.91477</v>
+        <v>33.87402</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.84814</v>
+        <v>16.77754</v>
       </c>
       <c r="D7" t="n">
-        <v>15.80492</v>
+        <v>15.71786</v>
       </c>
       <c r="E7" t="n">
-        <v>16.07611</v>
+        <v>16.16646</v>
       </c>
       <c r="F7" t="n">
-        <v>21.52172</v>
+        <v>21.87828</v>
       </c>
       <c r="G7" t="n">
-        <v>33.90178</v>
+        <v>33.78305</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.35717</v>
+        <v>16.50441</v>
       </c>
       <c r="D8" t="n">
-        <v>15.88279</v>
+        <v>15.98282</v>
       </c>
       <c r="E8" t="n">
-        <v>16.23384</v>
+        <v>16.09495</v>
       </c>
       <c r="F8" t="n">
-        <v>21.76065</v>
+        <v>21.73454</v>
       </c>
       <c r="G8" t="n">
-        <v>34.14069</v>
+        <v>33.95086</v>
       </c>
     </row>
   </sheetData>
